--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.0586,0.9186,0.0380,0.0063</t>
-  </si>
-  <si>
-    <t>0.3622,0.2045,0.0311,0.2547</t>
-  </si>
-  <si>
-    <t>0.2277,0.7330,0.0552,0.0185</t>
-  </si>
-  <si>
-    <t>0.6637,0.1144,0.1398,0.0181</t>
-  </si>
-  <si>
-    <t>0.4029,0.3845,0.0195,0.0848</t>
-  </si>
-  <si>
-    <t>0.2880,0.5634,0.0191,0.0611</t>
-  </si>
-  <si>
-    <t>0.3288,0.6310,0.0409,0.0209</t>
-  </si>
-  <si>
-    <t>0.4336,0.4440,0.0289,0.0390</t>
-  </si>
-  <si>
-    <t>0.2315,0.7152,0.0286,0.0275</t>
-  </si>
-  <si>
-    <t>0.2698,0.6746,0.0382,0.0294</t>
-  </si>
-  <si>
-    <t>0.2787,0.5757,0.0200,0.0668</t>
-  </si>
-  <si>
-    <t>0.4524,0.4609,0.0280,0.0269</t>
-  </si>
-  <si>
-    <t>0.1319,0.7661,0.1156,0.0042</t>
-  </si>
-  <si>
-    <t>0.0447,0.8825,0.1250,0.0027</t>
-  </si>
-  <si>
-    <t>0.1249,0.5592,0.3156,0.0043</t>
-  </si>
-  <si>
-    <t>0.1618,0.2499,0.4896,0.0035</t>
-  </si>
-  <si>
-    <t>0.2914,0.5333,0.1288,0.0057</t>
-  </si>
-  <si>
-    <t>0.0141,0.9747,0.0199,0.0016</t>
-  </si>
-  <si>
-    <t>0.0205,0.9634,0.0277,0.0026</t>
-  </si>
-  <si>
-    <t>0.0175,0.9696,0.0227,0.0019</t>
-  </si>
-  <si>
-    <t>0.0194,0.9654,0.0266,0.0026</t>
-  </si>
-  <si>
-    <t>0.0051,0.9890,0.0126,0.0007</t>
-  </si>
-  <si>
-    <t>0.2490,0.4648,0.2458,0.0059</t>
-  </si>
-  <si>
-    <t>0.3218,0.1886,0.3529,0.0025</t>
-  </si>
-  <si>
-    <t>0.0858,0.0233,0.8691,0.0012</t>
-  </si>
-  <si>
-    <t>0.4159,0.0805,0.4386,0.0044</t>
-  </si>
-  <si>
-    <t>0.3555,0.0226,0.6222,0.0036</t>
-  </si>
-  <si>
-    <t>0.4582,0.0213,0.5468,0.0037</t>
-  </si>
-  <si>
-    <t>0.0241,0.0982,0.9086,0.0011</t>
-  </si>
-  <si>
-    <t>0.0115,0.9726,0.0390,0.0016</t>
-  </si>
-  <si>
-    <t>0.2609,0.6363,0.1065,0.0077</t>
-  </si>
-  <si>
-    <t>0.0000,0.2334,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.1123,0.6353,0.2459,0.0028</t>
-  </si>
-  <si>
-    <t>0.1911,0.7502,0.0923,0.0135</t>
-  </si>
-  <si>
-    <t>0.1321,0.7870,0.1181,0.0120</t>
-  </si>
-  <si>
-    <t>0.0662,0.9134,0.0293,0.0066</t>
-  </si>
-  <si>
-    <t>0.0062,0.9856,0.0216,0.0009</t>
-  </si>
-  <si>
-    <t>0.0061,0.9746,0.0670,0.0004</t>
-  </si>
-  <si>
-    <t>0.3387,0.0374,0.5795,0.0031</t>
-  </si>
-  <si>
-    <t>0.0296,0.8541,0.2542,0.0022</t>
-  </si>
-  <si>
-    <t>0.3576,0.0275,0.6096,0.0046</t>
-  </si>
-  <si>
-    <t>0.0303,0.6687,0.5274,0.0021</t>
-  </si>
-  <si>
-    <t>0.0006,0.9981,0.0061,0.0000</t>
-  </si>
-  <si>
-    <t>0.0509,0.1732,0.8065,0.0032</t>
-  </si>
-  <si>
-    <t>0.3709,0.5198,0.0967,0.0221</t>
-  </si>
-  <si>
-    <t>0.0100,0.9787,0.0254,0.0010</t>
-  </si>
-  <si>
-    <t>0.0118,0.9709,0.0421,0.0008</t>
-  </si>
-  <si>
-    <t>0.0034,0.9919,0.0117,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.4296,0.9845,0.0001</t>
-  </si>
-  <si>
-    <t>0.0098,0.1464,0.9374,0.0006</t>
-  </si>
-  <si>
-    <t>0.1417,0.0799,0.7330,0.0056</t>
-  </si>
-  <si>
-    <t>0.3991,0.0156,0.6110,0.0036</t>
-  </si>
-  <si>
-    <t>0.0143,0.4915,0.8140,0.0015</t>
-  </si>
-  <si>
-    <t>0.0959,0.1860,0.6494,0.0022</t>
-  </si>
-  <si>
-    <t>0.1358,0.8419,0.0400,0.0124</t>
-  </si>
-  <si>
-    <t>0.2739,0.6577,0.0416,0.0367</t>
-  </si>
-  <si>
-    <t>0.3458,0.5781,0.0395,0.0351</t>
-  </si>
-  <si>
-    <t>0.0013,0.1060,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.2717,0.6825,0.0400,0.0250</t>
-  </si>
-  <si>
-    <t>0.2119,0.7375,0.0330,0.0289</t>
-  </si>
-  <si>
-    <t>0.1863,0.7919,0.0393,0.0163</t>
-  </si>
-  <si>
-    <t>0.0007,0.9830,0.2693,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0565,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0141,0.5437,0.7116,0.0009</t>
-  </si>
-  <si>
-    <t>0.0111,0.6350,0.7016,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0333,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0084,0.9800,0.0294,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.2503,0.0655,0.6314,0.0037</t>
-  </si>
-  <si>
-    <t>0.1596,0.6434,0.2050,0.0061</t>
-  </si>
-  <si>
-    <t>0.0013,0.4871,0.9737,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.9446,0.5330,0.0002</t>
-  </si>
-  <si>
-    <t>0.0346,0.7181,0.3647,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.9968,0.0162,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9862,0.2745,0.0001</t>
-  </si>
-  <si>
-    <t>0.3551,0.5169,0.0911,0.0382</t>
-  </si>
-  <si>
-    <t>0.1462,0.5071,0.0130,0.4024</t>
-  </si>
-  <si>
-    <t>0.1578,0.3477,0.0157,0.5825</t>
-  </si>
-  <si>
-    <t>0.2958,0.5416,0.0431,0.0934</t>
-  </si>
-  <si>
-    <t>0.2951,0.5393,0.0474,0.0857</t>
-  </si>
-  <si>
-    <t>0.2334,0.5739,0.0465,0.1657</t>
-  </si>
-  <si>
-    <t>0.0079,0.9572,0.1388,0.0007</t>
-  </si>
-  <si>
-    <t>0.0019,0.9677,0.3217,0.0003</t>
-  </si>
-  <si>
-    <t>0.0088,0.8408,0.5233,0.0010</t>
-  </si>
-  <si>
-    <t>0.0070,0.8629,0.4770,0.0009</t>
-  </si>
-  <si>
-    <t>0.0016,0.9794,0.2056,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9665,0.2010,0.0004</t>
-  </si>
-  <si>
-    <t>0.4100,0.5460,0.0504,0.0180</t>
-  </si>
-  <si>
-    <t>0.2258,0.7323,0.0359,0.0230</t>
-  </si>
-  <si>
-    <t>0.2576,0.6856,0.0369,0.0305</t>
-  </si>
-  <si>
-    <t>0.2287,0.7214,0.0406,0.0299</t>
-  </si>
-  <si>
-    <t>0.2674,0.6945,0.0429,0.0225</t>
-  </si>
-  <si>
-    <t>0.2419,0.6907,0.0403,0.0364</t>
-  </si>
-  <si>
-    <t>0.2380,0.6859,0.0344,0.0378</t>
-  </si>
-  <si>
-    <t>0.1341,0.8406,0.0343,0.0173</t>
-  </si>
-  <si>
-    <t>0.2964,0.5227,0.0210,0.0804</t>
-  </si>
-  <si>
-    <t>0.3402,0.5921,0.0379,0.0300</t>
-  </si>
-  <si>
-    <t>0.3484,0.4898,0.0293,0.0814</t>
-  </si>
-  <si>
-    <t>0.3953,0.4718,0.0260,0.0483</t>
-  </si>
-  <si>
-    <t>0.3526,0.4942,0.0266,0.0694</t>
-  </si>
-  <si>
-    <t>0.2180,0.7202,0.0352,0.0361</t>
-  </si>
-  <si>
-    <t>0.2792,0.6440,0.0297,0.0370</t>
-  </si>
-  <si>
-    <t>0.4546,0.3021,0.0225,0.0961</t>
-  </si>
-  <si>
-    <t>0.0001,0.0374,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.4688,0.0296,0.5014,0.0025</t>
-  </si>
-  <si>
-    <t>0.1622,0.7551,0.0965,0.0062</t>
-  </si>
-  <si>
-    <t>0.3160,0.0712,0.5238,0.0031</t>
-  </si>
-  <si>
-    <t>0.0099,0.9818,0.0150,0.0016</t>
-  </si>
-  <si>
-    <t>0.0077,0.9852,0.0134,0.0016</t>
-  </si>
-  <si>
-    <t>0.0134,0.9772,0.0154,0.0022</t>
-  </si>
-  <si>
-    <t>0.0285,0.9549,0.0263,0.0044</t>
-  </si>
-  <si>
-    <t>0.0234,0.9614,0.0250,0.0039</t>
-  </si>
-  <si>
-    <t>0.0047,0.9911,0.0074,0.0010</t>
-  </si>
-  <si>
-    <t>0.0408,0.9423,0.0254,0.0054</t>
-  </si>
-  <si>
-    <t>0.2551,0.5416,0.1641,0.0075</t>
-  </si>
-  <si>
-    <t>0.3293,0.3020,0.2881,0.0049</t>
-  </si>
-  <si>
-    <t>0.1115,0.8116,0.0777,0.0041</t>
-  </si>
-  <si>
-    <t>0.1825,0.7250,0.0920,0.0082</t>
-  </si>
-  <si>
-    <t>0.2597,0.5894,0.1358,0.0126</t>
-  </si>
-  <si>
-    <t>0.0020,0.9948,0.0099,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.9907,0.0123,0.0004</t>
-  </si>
-  <si>
-    <t>0.0206,0.9680,0.0185,0.0020</t>
-  </si>
-  <si>
-    <t>0.0006,0.9930,0.1240,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.9837,0.0233,0.0006</t>
-  </si>
-  <si>
-    <t>0.1335,0.8391,0.0464,0.0077</t>
-  </si>
-  <si>
-    <t>0.0704,0.9006,0.0444,0.0060</t>
-  </si>
-  <si>
-    <t>0.1066,0.8650,0.0462,0.0117</t>
-  </si>
-  <si>
-    <t>0.3022,0.5979,0.0352,0.0493</t>
-  </si>
-  <si>
-    <t>0.2581,0.6997,0.0376,0.0230</t>
-  </si>
-  <si>
-    <t>0.1496,0.8335,0.0344,0.0113</t>
-  </si>
-  <si>
-    <t>0.3494,0.5697,0.0358,0.0346</t>
-  </si>
-  <si>
-    <t>0.1375,0.8329,0.0469,0.0148</t>
-  </si>
-  <si>
-    <t>0.2322,0.7352,0.0452,0.0184</t>
-  </si>
-  <si>
-    <t>0.2900,0.6480,0.0347,0.0298</t>
-  </si>
-  <si>
-    <t>0.0140,0.8837,0.2326,0.0009</t>
-  </si>
-  <si>
-    <t>0.0393,0.3658,0.6529,0.0011</t>
-  </si>
-  <si>
-    <t>0.0266,0.6960,0.5443,0.0025</t>
-  </si>
-  <si>
-    <t>0.0481,0.5971,0.4853,0.0025</t>
-  </si>
-  <si>
-    <t>0.3311,0.4510,0.1354,0.0052</t>
-  </si>
-  <si>
-    <t>0.2457,0.6323,0.0983,0.0066</t>
-  </si>
-  <si>
-    <t>0.2540,0.3490,0.3391,0.0053</t>
-  </si>
-  <si>
-    <t>0.3394,0.3690,0.1922,0.0044</t>
-  </si>
-  <si>
-    <t>0.2837,0.6229,0.0530,0.0549</t>
-  </si>
-  <si>
-    <t>0.0689,0.1123,0.0054,0.9094</t>
-  </si>
-  <si>
-    <t>0.1433,0.3732,0.0163,0.6189</t>
-  </si>
-  <si>
-    <t>0.3790,0.3750,0.0562,0.1201</t>
-  </si>
-  <si>
-    <t>0.0002,0.9710,0.7482,0.0000</t>
-  </si>
-  <si>
-    <t>0.1751,0.7665,0.0271,0.0345</t>
-  </si>
-  <si>
-    <t>0.0387,0.9427,0.0291,0.0063</t>
-  </si>
-  <si>
-    <t>0.3339,0.6094,0.0463,0.0244</t>
-  </si>
-  <si>
-    <t>0.1552,0.8154,0.0504,0.0139</t>
-  </si>
-  <si>
-    <t>0.3127,0.6444,0.0613,0.0135</t>
-  </si>
-  <si>
-    <t>0.6650,0.1050,0.0867,0.0392</t>
-  </si>
-  <si>
-    <t>0.4200,0.5056,0.0587,0.0276</t>
-  </si>
-  <si>
-    <t>0.0055,0.3003,0.9606,0.0026</t>
-  </si>
-  <si>
-    <t>0.7744,0.0773,0.0804,0.0139</t>
-  </si>
-  <si>
-    <t>0.6533,0.1748,0.0662,0.0289</t>
-  </si>
-  <si>
-    <t>0.0251,0.9576,0.0311,0.0028</t>
-  </si>
-  <si>
-    <t>0.1985,0.7644,0.0636,0.0154</t>
-  </si>
-  <si>
-    <t>0.2054,0.7194,0.0981,0.0107</t>
-  </si>
-  <si>
-    <t>0.0368,0.9452,0.0307,0.0035</t>
-  </si>
-  <si>
-    <t>0.1798,0.7772,0.0698,0.0093</t>
-  </si>
-  <si>
-    <t>0.1237,0.8423,0.0577,0.0094</t>
-  </si>
-  <si>
-    <t>0.2214,0.7335,0.0341,0.0246</t>
-  </si>
-  <si>
-    <t>0.2732,0.6848,0.0485,0.0216</t>
-  </si>
-  <si>
-    <t>0.3429,0.6114,0.0385,0.0210</t>
-  </si>
-  <si>
-    <t>0.3250,0.6096,0.0500,0.0295</t>
-  </si>
-  <si>
-    <t>0.3454,0.5936,0.0474,0.0274</t>
-  </si>
-  <si>
-    <t>0.1463,0.8137,0.0326,0.0292</t>
-  </si>
-  <si>
-    <t>0.3481,0.5486,0.0352,0.0462</t>
-  </si>
-  <si>
-    <t>0.3184,0.6476,0.0356,0.0194</t>
-  </si>
-  <si>
-    <t>0.0332,0.9520,0.0226,0.0031</t>
-  </si>
-  <si>
-    <t>0.0773,0.8972,0.0314,0.0166</t>
-  </si>
-  <si>
-    <t>0.1439,0.8277,0.0502,0.0091</t>
-  </si>
-  <si>
-    <t>0.1606,0.5344,0.3474,0.0094</t>
-  </si>
-  <si>
-    <t>0.1669,0.8145,0.0374,0.0122</t>
-  </si>
-  <si>
-    <t>0.1885,0.7959,0.0378,0.0112</t>
-  </si>
-  <si>
-    <t>0.2262,0.7485,0.0365,0.0160</t>
-  </si>
-  <si>
-    <t>0.0679,0.9139,0.0240,0.0109</t>
-  </si>
-  <si>
-    <t>0.0000,0.5577,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.2211,0.7428,0.0548,0.0182</t>
-  </si>
-  <si>
-    <t>0.0285,0.0537,0.9130,0.0006</t>
-  </si>
-  <si>
-    <t>0.0154,0.4434,0.8191,0.0017</t>
-  </si>
-  <si>
-    <t>0.1880,0.3591,0.4572,0.0071</t>
-  </si>
-  <si>
-    <t>0.0002,0.1740,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0180,0.0970,0.9343,0.0010</t>
-  </si>
-  <si>
-    <t>0.0138,0.0108,0.9750,0.0005</t>
-  </si>
-  <si>
-    <t>0.1363,0.0853,0.7325,0.0046</t>
-  </si>
-  <si>
-    <t>0.3325,0.3845,0.2141,0.0075</t>
-  </si>
-  <si>
-    <t>0.1614,0.0816,0.7191,0.0053</t>
-  </si>
-  <si>
-    <t>0.3003,0.3434,0.2731,0.0046</t>
-  </si>
-  <si>
-    <t>0.1692,0.6419,0.1248,0.0029</t>
-  </si>
-  <si>
-    <t>0.1206,0.7781,0.1060,0.0050</t>
-  </si>
-  <si>
-    <t>0.1522,0.7559,0.1038,0.0073</t>
-  </si>
-  <si>
-    <t>0.1797,0.7166,0.1150,0.0080</t>
-  </si>
-  <si>
-    <t>0.2905,0.4643,0.1909,0.0058</t>
-  </si>
-  <si>
-    <t>0.0401,0.9457,0.0195,0.0055</t>
-  </si>
-  <si>
-    <t>0.0573,0.9262,0.0246,0.0054</t>
-  </si>
-  <si>
-    <t>0.0288,0.9577,0.0198,0.0037</t>
-  </si>
-  <si>
-    <t>0.1083,0.8608,0.0284,0.0240</t>
-  </si>
-  <si>
-    <t>0.1098,0.8700,0.0270,0.0144</t>
-  </si>
-  <si>
-    <t>0.2470,0.5635,0.1280,0.0035</t>
-  </si>
-  <si>
-    <t>0.2666,0.6203,0.1025,0.0066</t>
-  </si>
-  <si>
-    <t>0.2237,0.6409,0.1181,0.0066</t>
-  </si>
-  <si>
-    <t>0.3894,0.1554,0.3621,0.0042</t>
-  </si>
-  <si>
-    <t>0.2069,0.5646,0.1591,0.0034</t>
-  </si>
-  <si>
-    <t>0.0419,0.5571,0.5998,0.0038</t>
-  </si>
-  <si>
-    <t>0.0715,0.2621,0.6851,0.0031</t>
-  </si>
-  <si>
-    <t>0.0878,0.6112,0.2770,0.0022</t>
-  </si>
-  <si>
-    <t>0.0691,0.6407,0.2917,0.0023</t>
-  </si>
-  <si>
-    <t>0.0718,0.4684,0.4132,0.0018</t>
-  </si>
-  <si>
-    <t>0.2616,0.6399,0.0236,0.0488</t>
-  </si>
-  <si>
-    <t>0.1871,0.7733,0.0309,0.0268</t>
-  </si>
-  <si>
-    <t>0.1082,0.8560,0.0254,0.0276</t>
-  </si>
-  <si>
-    <t>0.1876,0.7730,0.0350,0.0259</t>
-  </si>
-  <si>
-    <t>0.1837,0.7561,0.0258,0.0400</t>
-  </si>
-  <si>
-    <t>0.1839,0.7493,0.0243,0.0382</t>
-  </si>
-  <si>
-    <t>0.2272,0.7130,0.0320,0.0338</t>
-  </si>
-  <si>
-    <t>0.2383,0.7066,0.0320,0.0284</t>
-  </si>
-  <si>
-    <t>0.0772,0.2777,0.7425,0.0079</t>
-  </si>
-  <si>
-    <t>0.1392,0.8028,0.0711,0.0064</t>
-  </si>
-  <si>
-    <t>0.1104,0.8524,0.0578,0.0086</t>
-  </si>
-  <si>
-    <t>0.1023,0.1447,0.6979,0.0024</t>
-  </si>
-  <si>
-    <t>0.0013,0.3865,0.9697,0.0002</t>
-  </si>
-  <si>
-    <t>0.1240,0.2415,0.5908,0.0049</t>
-  </si>
-  <si>
-    <t>0.0022,0.0323,0.9912,0.0001</t>
-  </si>
-  <si>
-    <t>0.1249,0.2488,0.6049,0.0046</t>
-  </si>
-  <si>
-    <t>0.0000,0.0221,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.1988,0.0497,0.7000,0.0040</t>
-  </si>
-  <si>
-    <t>0.0258,0.5129,0.7043,0.0023</t>
-  </si>
-  <si>
-    <t>0.4811,0.1574,0.2506,0.0040</t>
-  </si>
-  <si>
-    <t>0.2925,0.1538,0.4406,0.0042</t>
-  </si>
-  <si>
-    <t>0.2651,0.6102,0.1096,0.0089</t>
-  </si>
-  <si>
-    <t>0.2030,0.7510,0.0289,0.0284</t>
-  </si>
-  <si>
-    <t>0.2597,0.6964,0.0410,0.0234</t>
-  </si>
-  <si>
-    <t>0.3427,0.5829,0.0291,0.0290</t>
-  </si>
-  <si>
-    <t>0.2516,0.7159,0.0419,0.0182</t>
-  </si>
-  <si>
-    <t>0.1822,0.7244,0.0228,0.0667</t>
-  </si>
-  <si>
-    <t>0.3558,0.5714,0.0403,0.0334</t>
-  </si>
-  <si>
-    <t>0.2017,0.7412,0.0272,0.0321</t>
-  </si>
-  <si>
-    <t>0.2550,0.6509,0.0304,0.0466</t>
-  </si>
-  <si>
-    <t>0.1255,0.5875,0.2387,0.0038</t>
-  </si>
-  <si>
-    <t>0.0025,0.2068,0.9724,0.0002</t>
-  </si>
-  <si>
-    <t>0.0070,0.5481,0.8498,0.0009</t>
-  </si>
-  <si>
-    <t>0.3845,0.2448,0.2508,0.0038</t>
-  </si>
-  <si>
-    <t>0.0069,0.1526,0.9534,0.0005</t>
-  </si>
-  <si>
-    <t>0.5463,0.0633,0.3806,0.0057</t>
-  </si>
-  <si>
-    <t>0.1039,0.5193,0.3421,0.0020</t>
-  </si>
-  <si>
-    <t>0.1518,0.0176,0.8122,0.0024</t>
-  </si>
-  <si>
-    <t>0.5999,0.2407,0.0498,0.0293</t>
-  </si>
-  <si>
-    <t>0.0977,0.7592,0.0198,0.2407</t>
-  </si>
-  <si>
-    <t>0.2107,0.6520,0.0266,0.0901</t>
-  </si>
-  <si>
-    <t>0.3163,0.1781,0.0221,0.3381</t>
-  </si>
-  <si>
-    <t>0.0675,0.3140,0.0052,0.8372</t>
-  </si>
-  <si>
-    <t>0.5916,0.1862,0.1713,0.0153</t>
+    <t>0.0929,0.8708,0.0568,0.0068</t>
+  </si>
+  <si>
+    <t>0.2938,0.2749,0.0196,0.2861</t>
+  </si>
+  <si>
+    <t>0.2424,0.7245,0.0540,0.0156</t>
+  </si>
+  <si>
+    <t>0.6532,0.0931,0.2109,0.0110</t>
+  </si>
+  <si>
+    <t>0.3321,0.5153,0.0199,0.0618</t>
+  </si>
+  <si>
+    <t>0.3295,0.5168,0.0199,0.0552</t>
+  </si>
+  <si>
+    <t>0.2340,0.7458,0.0376,0.0140</t>
+  </si>
+  <si>
+    <t>0.4708,0.3950,0.0338,0.0440</t>
+  </si>
+  <si>
+    <t>0.2414,0.6697,0.0280,0.0438</t>
+  </si>
+  <si>
+    <t>0.2439,0.7055,0.0361,0.0281</t>
+  </si>
+  <si>
+    <t>0.3289,0.5865,0.0340,0.0371</t>
+  </si>
+  <si>
+    <t>0.3266,0.5650,0.0261,0.0450</t>
+  </si>
+  <si>
+    <t>0.1873,0.7083,0.0995,0.0048</t>
+  </si>
+  <si>
+    <t>0.1278,0.5002,0.3663,0.0043</t>
+  </si>
+  <si>
+    <t>0.0834,0.7790,0.1754,0.0052</t>
+  </si>
+  <si>
+    <t>0.2992,0.3205,0.2644,0.0041</t>
+  </si>
+  <si>
+    <t>0.1841,0.7332,0.0855,0.0064</t>
+  </si>
+  <si>
+    <t>0.0194,0.9649,0.0280,0.0015</t>
+  </si>
+  <si>
+    <t>0.0100,0.9795,0.0210,0.0013</t>
+  </si>
+  <si>
+    <t>0.0156,0.9736,0.0187,0.0021</t>
+  </si>
+  <si>
+    <t>0.0184,0.9661,0.0280,0.0025</t>
+  </si>
+  <si>
+    <t>0.0042,0.9898,0.0153,0.0006</t>
+  </si>
+  <si>
+    <t>0.1729,0.7035,0.1202,0.0072</t>
+  </si>
+  <si>
+    <t>0.1589,0.5955,0.1982,0.0031</t>
+  </si>
+  <si>
+    <t>0.1527,0.0433,0.7570,0.0024</t>
+  </si>
+  <si>
+    <t>0.3389,0.3087,0.2241,0.0036</t>
+  </si>
+  <si>
+    <t>0.3446,0.0250,0.6269,0.0039</t>
+  </si>
+  <si>
+    <t>0.3988,0.0249,0.5838,0.0040</t>
+  </si>
+  <si>
+    <t>0.0482,0.1057,0.8260,0.0012</t>
+  </si>
+  <si>
+    <t>0.0232,0.9569,0.0382,0.0031</t>
+  </si>
+  <si>
+    <t>0.2667,0.5859,0.1347,0.0066</t>
+  </si>
+  <si>
+    <t>0.0000,0.4486,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0251,0.9472,0.0489,0.0009</t>
+  </si>
+  <si>
+    <t>0.2149,0.7311,0.0774,0.0272</t>
+  </si>
+  <si>
+    <t>0.1351,0.7993,0.0946,0.0103</t>
+  </si>
+  <si>
+    <t>0.0689,0.9106,0.0317,0.0063</t>
+  </si>
+  <si>
+    <t>0.0112,0.9740,0.0359,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.9647,0.2303,0.0004</t>
+  </si>
+  <si>
+    <t>0.2197,0.1116,0.5398,0.0038</t>
+  </si>
+  <si>
+    <t>0.0987,0.4914,0.4225,0.0043</t>
+  </si>
+  <si>
+    <t>0.5190,0.0267,0.4781,0.0035</t>
+  </si>
+  <si>
+    <t>0.0501,0.7714,0.2490,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.9936,0.0107,0.0001</t>
+  </si>
+  <si>
+    <t>0.0225,0.1258,0.9109,0.0017</t>
+  </si>
+  <si>
+    <t>0.3184,0.6016,0.0633,0.0270</t>
+  </si>
+  <si>
+    <t>0.0106,0.9800,0.0186,0.0011</t>
+  </si>
+  <si>
+    <t>0.0036,0.9916,0.0117,0.0003</t>
+  </si>
+  <si>
+    <t>0.0075,0.9856,0.0133,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.0278,0.9883,0.0004</t>
+  </si>
+  <si>
+    <t>0.0304,0.0688,0.9083,0.0016</t>
+  </si>
+  <si>
+    <t>0.3263,0.1524,0.4189,0.0061</t>
+  </si>
+  <si>
+    <t>0.3629,0.0136,0.6467,0.0035</t>
+  </si>
+  <si>
+    <t>0.0049,0.5960,0.8865,0.0007</t>
+  </si>
+  <si>
+    <t>0.0202,0.1601,0.8862,0.0009</t>
+  </si>
+  <si>
+    <t>0.1753,0.8028,0.0415,0.0142</t>
+  </si>
+  <si>
+    <t>0.3076,0.6304,0.0487,0.0314</t>
+  </si>
+  <si>
+    <t>0.2728,0.6537,0.0285,0.0376</t>
+  </si>
+  <si>
+    <t>0.0026,0.2554,0.9786,0.0009</t>
+  </si>
+  <si>
+    <t>0.2786,0.6719,0.0400,0.0255</t>
+  </si>
+  <si>
+    <t>0.2052,0.6905,0.0220,0.0615</t>
+  </si>
+  <si>
+    <t>0.2426,0.7094,0.0394,0.0299</t>
+  </si>
+  <si>
+    <t>0.0025,0.9095,0.5629,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0475,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0137,0.1597,0.9153,0.0008</t>
+  </si>
+  <si>
+    <t>0.0025,0.9598,0.2972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0269,0.9886,0.0002</t>
+  </si>
+  <si>
+    <t>0.0077,0.9807,0.0300,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2659,0.1159,0.5608,0.0062</t>
+  </si>
+  <si>
+    <t>0.1807,0.6871,0.1249,0.0049</t>
+  </si>
+  <si>
+    <t>0.0020,0.8034,0.8905,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9796,0.3614,0.0001</t>
+  </si>
+  <si>
+    <t>0.0137,0.8171,0.4300,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.9976,0.0078,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9910,0.2217,0.0000</t>
+  </si>
+  <si>
+    <t>0.6663,0.1046,0.1826,0.0136</t>
+  </si>
+  <si>
+    <t>0.2269,0.2331,0.0156,0.4672</t>
+  </si>
+  <si>
+    <t>0.2800,0.0859,0.0133,0.5260</t>
+  </si>
+  <si>
+    <t>0.3003,0.5212,0.0412,0.1001</t>
+  </si>
+  <si>
+    <t>0.1506,0.7760,0.0506,0.0517</t>
+  </si>
+  <si>
+    <t>0.3533,0.3664,0.0402,0.1608</t>
+  </si>
+  <si>
+    <t>0.0025,0.9645,0.2926,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9597,0.4711,0.0002</t>
+  </si>
+  <si>
+    <t>0.0079,0.8383,0.5040,0.0008</t>
+  </si>
+  <si>
+    <t>0.0453,0.5997,0.4457,0.0024</t>
+  </si>
+  <si>
+    <t>0.0014,0.9799,0.2101,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.9005,0.3783,0.0008</t>
+  </si>
+  <si>
+    <t>0.2911,0.6472,0.0369,0.0285</t>
+  </si>
+  <si>
+    <t>0.2395,0.7250,0.0328,0.0197</t>
+  </si>
+  <si>
+    <t>0.2471,0.7182,0.0336,0.0210</t>
+  </si>
+  <si>
+    <t>0.2764,0.6339,0.0358,0.0436</t>
+  </si>
+  <si>
+    <t>0.2417,0.7148,0.0435,0.0242</t>
+  </si>
+  <si>
+    <t>0.3405,0.5101,0.0260,0.0644</t>
+  </si>
+  <si>
+    <t>0.3070,0.6175,0.0421,0.0328</t>
+  </si>
+  <si>
+    <t>0.1943,0.7659,0.0307,0.0247</t>
+  </si>
+  <si>
+    <t>0.2522,0.5496,0.0241,0.1227</t>
+  </si>
+  <si>
+    <t>0.3880,0.5433,0.0340,0.0264</t>
+  </si>
+  <si>
+    <t>0.3798,0.5008,0.0280,0.0487</t>
+  </si>
+  <si>
+    <t>0.4031,0.4734,0.0297,0.0458</t>
+  </si>
+  <si>
+    <t>0.3764,0.4983,0.0270,0.0518</t>
+  </si>
+  <si>
+    <t>0.3114,0.6112,0.0324,0.0374</t>
+  </si>
+  <si>
+    <t>0.1896,0.7461,0.0230,0.0357</t>
+  </si>
+  <si>
+    <t>0.4426,0.3396,0.0295,0.0935</t>
+  </si>
+  <si>
+    <t>0.0002,0.0499,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.2589,0.0392,0.6452,0.0023</t>
+  </si>
+  <si>
+    <t>0.3654,0.3687,0.2013,0.0055</t>
+  </si>
+  <si>
+    <t>0.3056,0.0829,0.5312,0.0032</t>
+  </si>
+  <si>
+    <t>0.0078,0.9852,0.0129,0.0019</t>
+  </si>
+  <si>
+    <t>0.0070,0.9863,0.0128,0.0019</t>
+  </si>
+  <si>
+    <t>0.0240,0.9649,0.0151,0.0034</t>
+  </si>
+  <si>
+    <t>0.0336,0.9481,0.0285,0.0046</t>
+  </si>
+  <si>
+    <t>0.0089,0.9832,0.0144,0.0020</t>
+  </si>
+  <si>
+    <t>0.0027,0.9938,0.0081,0.0007</t>
+  </si>
+  <si>
+    <t>0.0308,0.9507,0.0290,0.0040</t>
+  </si>
+  <si>
+    <t>0.1982,0.6544,0.1118,0.0047</t>
+  </si>
+  <si>
+    <t>0.2337,0.1226,0.5613,0.0039</t>
+  </si>
+  <si>
+    <t>0.2732,0.5238,0.1439,0.0057</t>
+  </si>
+  <si>
+    <t>0.0779,0.8714,0.0783,0.0052</t>
+  </si>
+  <si>
+    <t>0.1032,0.8472,0.0773,0.0086</t>
+  </si>
+  <si>
+    <t>0.0060,0.9872,0.0154,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.9964,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0570,0.9220,0.0342,0.0048</t>
+  </si>
+  <si>
+    <t>0.0009,0.9930,0.0738,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9916,0.0182,0.0004</t>
+  </si>
+  <si>
+    <t>0.0920,0.8778,0.0468,0.0061</t>
+  </si>
+  <si>
+    <t>0.0730,0.8983,0.0444,0.0075</t>
+  </si>
+  <si>
+    <t>0.1147,0.8458,0.0644,0.0113</t>
+  </si>
+  <si>
+    <t>0.2544,0.6671,0.0352,0.0403</t>
+  </si>
+  <si>
+    <t>0.2689,0.6657,0.0303,0.0314</t>
+  </si>
+  <si>
+    <t>0.1012,0.8799,0.0232,0.0136</t>
+  </si>
+  <si>
+    <t>0.2498,0.6704,0.0269,0.0418</t>
+  </si>
+  <si>
+    <t>0.1838,0.7794,0.0605,0.0140</t>
+  </si>
+  <si>
+    <t>0.2999,0.6578,0.0404,0.0224</t>
+  </si>
+  <si>
+    <t>0.3332,0.6258,0.0502,0.0201</t>
+  </si>
+  <si>
+    <t>0.0126,0.7538,0.5361,0.0011</t>
+  </si>
+  <si>
+    <t>0.0155,0.6075,0.6445,0.0010</t>
+  </si>
+  <si>
+    <t>0.0165,0.6680,0.6745,0.0021</t>
+  </si>
+  <si>
+    <t>0.0401,0.3813,0.6938,0.0021</t>
+  </si>
+  <si>
+    <t>0.2406,0.6269,0.1006,0.0057</t>
+  </si>
+  <si>
+    <t>0.1207,0.7503,0.1385,0.0051</t>
+  </si>
+  <si>
+    <t>0.1986,0.2477,0.4818,0.0048</t>
+  </si>
+  <si>
+    <t>0.1641,0.7370,0.0967,0.0050</t>
+  </si>
+  <si>
+    <t>0.3864,0.4716,0.0587,0.0707</t>
+  </si>
+  <si>
+    <t>0.0489,0.2968,0.0052,0.9022</t>
+  </si>
+  <si>
+    <t>0.1278,0.1908,0.0139,0.7725</t>
+  </si>
+  <si>
+    <t>0.3255,0.4547,0.0397,0.1210</t>
+  </si>
+  <si>
+    <t>0.0005,0.9615,0.6697,0.0001</t>
+  </si>
+  <si>
+    <t>0.1674,0.8005,0.0317,0.0207</t>
+  </si>
+  <si>
+    <t>0.0278,0.9567,0.0234,0.0055</t>
+  </si>
+  <si>
+    <t>0.2479,0.7155,0.0439,0.0209</t>
+  </si>
+  <si>
+    <t>0.1853,0.7815,0.0611,0.0137</t>
+  </si>
+  <si>
+    <t>0.2029,0.7493,0.0718,0.0115</t>
+  </si>
+  <si>
+    <t>0.6718,0.1374,0.1204,0.0176</t>
+  </si>
+  <si>
+    <t>0.3426,0.5921,0.0681,0.0290</t>
+  </si>
+  <si>
+    <t>0.0053,0.4215,0.9509,0.0034</t>
+  </si>
+  <si>
+    <t>0.7520,0.0875,0.1091,0.0127</t>
+  </si>
+  <si>
+    <t>0.7270,0.1394,0.0879,0.0117</t>
+  </si>
+  <si>
+    <t>0.0389,0.9340,0.0501,0.0040</t>
+  </si>
+  <si>
+    <t>0.2171,0.7384,0.0776,0.0121</t>
+  </si>
+  <si>
+    <t>0.1842,0.7666,0.0801,0.0106</t>
+  </si>
+  <si>
+    <t>0.0468,0.9320,0.0361,0.0036</t>
+  </si>
+  <si>
+    <t>0.3816,0.4633,0.1132,0.0058</t>
+  </si>
+  <si>
+    <t>0.1105,0.8611,0.0466,0.0089</t>
+  </si>
+  <si>
+    <t>0.3939,0.5129,0.0363,0.0333</t>
+  </si>
+  <si>
+    <t>0.2729,0.6381,0.0308,0.0414</t>
+  </si>
+  <si>
+    <t>0.2893,0.6710,0.0440,0.0210</t>
+  </si>
+  <si>
+    <t>0.3093,0.5901,0.0346,0.0475</t>
+  </si>
+  <si>
+    <t>0.3486,0.5989,0.0413,0.0237</t>
+  </si>
+  <si>
+    <t>0.1677,0.8044,0.0401,0.0187</t>
+  </si>
+  <si>
+    <t>0.4395,0.4843,0.0451,0.0291</t>
+  </si>
+  <si>
+    <t>0.3355,0.5717,0.0285,0.0388</t>
+  </si>
+  <si>
+    <t>0.0743,0.9022,0.0380,0.0056</t>
+  </si>
+  <si>
+    <t>0.0792,0.8967,0.0328,0.0146</t>
+  </si>
+  <si>
+    <t>0.0697,0.9025,0.0445,0.0075</t>
+  </si>
+  <si>
+    <t>0.2708,0.5815,0.1422,0.0091</t>
+  </si>
+  <si>
+    <t>0.1130,0.8741,0.0267,0.0072</t>
+  </si>
+  <si>
+    <t>0.2105,0.7681,0.0437,0.0128</t>
+  </si>
+  <si>
+    <t>0.1910,0.7719,0.0392,0.0215</t>
+  </si>
+  <si>
+    <t>0.1116,0.8611,0.0361,0.0166</t>
+  </si>
+  <si>
+    <t>0.0001,0.4901,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.2619,0.6992,0.0635,0.0140</t>
+  </si>
+  <si>
+    <t>0.0233,0.0694,0.9183,0.0005</t>
+  </si>
+  <si>
+    <t>0.0170,0.2404,0.8840,0.0012</t>
+  </si>
+  <si>
+    <t>0.1467,0.2022,0.6224,0.0050</t>
+  </si>
+  <si>
+    <t>0.0004,0.0995,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0345,0.1438,0.8692,0.0019</t>
+  </si>
+  <si>
+    <t>0.0119,0.0331,0.9685,0.0006</t>
+  </si>
+  <si>
+    <t>0.0222,0.1118,0.9216,0.0019</t>
+  </si>
+  <si>
+    <t>0.1850,0.4191,0.3372,0.0053</t>
+  </si>
+  <si>
+    <t>0.4282,0.0598,0.4934,0.0077</t>
+  </si>
+  <si>
+    <t>0.2895,0.4772,0.1641,0.0049</t>
+  </si>
+  <si>
+    <t>0.1686,0.6516,0.1594,0.0048</t>
+  </si>
+  <si>
+    <t>0.0778,0.8102,0.1310,0.0038</t>
+  </si>
+  <si>
+    <t>0.2091,0.6626,0.1267,0.0093</t>
+  </si>
+  <si>
+    <t>0.2158,0.6906,0.1126,0.0127</t>
+  </si>
+  <si>
+    <t>0.1237,0.7611,0.1374,0.0065</t>
+  </si>
+  <si>
+    <t>0.0346,0.9521,0.0190,0.0046</t>
+  </si>
+  <si>
+    <t>0.0570,0.9218,0.0316,0.0055</t>
+  </si>
+  <si>
+    <t>0.0329,0.9523,0.0217,0.0041</t>
+  </si>
+  <si>
+    <t>0.1077,0.8562,0.0272,0.0296</t>
+  </si>
+  <si>
+    <t>0.1008,0.8765,0.0242,0.0170</t>
+  </si>
+  <si>
+    <t>0.1540,0.7180,0.0957,0.0026</t>
+  </si>
+  <si>
+    <t>0.2261,0.5997,0.1542,0.0063</t>
+  </si>
+  <si>
+    <t>0.1409,0.7882,0.0843,0.0058</t>
+  </si>
+  <si>
+    <t>0.3394,0.3721,0.1932,0.0045</t>
+  </si>
+  <si>
+    <t>0.2758,0.4744,0.1728,0.0046</t>
+  </si>
+  <si>
+    <t>0.0311,0.4873,0.7230,0.0031</t>
+  </si>
+  <si>
+    <t>0.1244,0.3419,0.4792,0.0039</t>
+  </si>
+  <si>
+    <t>0.1282,0.3427,0.4516,0.0033</t>
+  </si>
+  <si>
+    <t>0.1902,0.2000,0.4787,0.0033</t>
+  </si>
+  <si>
+    <t>0.0407,0.6169,0.3993,0.0016</t>
+  </si>
+  <si>
+    <t>0.2773,0.6278,0.0273,0.0462</t>
+  </si>
+  <si>
+    <t>0.1327,0.8380,0.0253,0.0225</t>
+  </si>
+  <si>
+    <t>0.1524,0.8128,0.0326,0.0237</t>
+  </si>
+  <si>
+    <t>0.2299,0.7282,0.0357,0.0252</t>
+  </si>
+  <si>
+    <t>0.1988,0.7584,0.0344,0.0277</t>
+  </si>
+  <si>
+    <t>0.2120,0.7180,0.0267,0.0377</t>
+  </si>
+  <si>
+    <t>0.1756,0.7639,0.0314,0.0423</t>
+  </si>
+  <si>
+    <t>0.3281,0.6251,0.0405,0.0212</t>
+  </si>
+  <si>
+    <t>0.1910,0.0804,0.6986,0.0077</t>
+  </si>
+  <si>
+    <t>0.1208,0.8311,0.0712,0.0081</t>
+  </si>
+  <si>
+    <t>0.0799,0.8887,0.0507,0.0054</t>
+  </si>
+  <si>
+    <t>0.0030,0.2195,0.9659,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.2180,0.9861,0.0002</t>
+  </si>
+  <si>
+    <t>0.1341,0.1132,0.7042,0.0061</t>
+  </si>
+  <si>
+    <t>0.0003,0.0253,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.1399,0.5069,0.3475,0.0049</t>
+  </si>
+  <si>
+    <t>0.0000,0.0237,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.2241,0.1054,0.5887,0.0051</t>
+  </si>
+  <si>
+    <t>0.0863,0.7843,0.1747,0.0050</t>
+  </si>
+  <si>
+    <t>0.4125,0.3686,0.1455,0.0077</t>
+  </si>
+  <si>
+    <t>0.3656,0.3165,0.2196,0.0059</t>
+  </si>
+  <si>
+    <t>0.3759,0.3959,0.1698,0.0071</t>
+  </si>
+  <si>
+    <t>0.1786,0.7825,0.0284,0.0255</t>
+  </si>
+  <si>
+    <t>0.3107,0.6115,0.0364,0.0340</t>
+  </si>
+  <si>
+    <t>0.2930,0.6028,0.0250,0.0445</t>
+  </si>
+  <si>
+    <t>0.1448,0.8047,0.0254,0.0338</t>
+  </si>
+  <si>
+    <t>0.3943,0.4569,0.0273,0.0540</t>
+  </si>
+  <si>
+    <t>0.2862,0.6430,0.0354,0.0337</t>
+  </si>
+  <si>
+    <t>0.1559,0.7980,0.0230,0.0304</t>
+  </si>
+  <si>
+    <t>0.2225,0.6707,0.0216,0.0553</t>
+  </si>
+  <si>
+    <t>0.0512,0.8348,0.1868,0.0039</t>
+  </si>
+  <si>
+    <t>0.0057,0.4641,0.8951,0.0006</t>
+  </si>
+  <si>
+    <t>0.0141,0.5456,0.7496,0.0014</t>
+  </si>
+  <si>
+    <t>0.1212,0.7703,0.0799,0.0016</t>
+  </si>
+  <si>
+    <t>0.0386,0.1292,0.8398,0.0013</t>
+  </si>
+  <si>
+    <t>0.2258,0.1415,0.5709,0.0065</t>
+  </si>
+  <si>
+    <t>0.1749,0.2453,0.4807,0.0030</t>
+  </si>
+  <si>
+    <t>0.3977,0.0127,0.6257,0.0024</t>
+  </si>
+  <si>
+    <t>0.4606,0.3357,0.0381,0.0556</t>
+  </si>
+  <si>
+    <t>0.1622,0.6128,0.0229,0.2695</t>
+  </si>
+  <si>
+    <t>0.2903,0.5414,0.0264,0.0783</t>
+  </si>
+  <si>
+    <t>0.5082,0.2145,0.0563,0.0990</t>
+  </si>
+  <si>
+    <t>0.0648,0.2536,0.0044,0.8627</t>
+  </si>
+  <si>
+    <t>0.5965,0.2073,0.1526,0.0108</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D6" t="s">
         <v>268</v>
@@ -2107,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D13" t="s">
         <v>275</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3311,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D99" t="s">
         <v>361</v>
@@ -3423,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
         <v>369</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3885,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
         <v>402</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
         <v>433</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5201,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
         <v>496</v>
@@ -5271,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D239" t="s">
         <v>501</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.0929,0.8708,0.0568,0.0068</t>
-  </si>
-  <si>
-    <t>0.2938,0.2749,0.0196,0.2861</t>
-  </si>
-  <si>
-    <t>0.2424,0.7245,0.0540,0.0156</t>
-  </si>
-  <si>
-    <t>0.6532,0.0931,0.2109,0.0110</t>
-  </si>
-  <si>
-    <t>0.3321,0.5153,0.0199,0.0618</t>
-  </si>
-  <si>
-    <t>0.3295,0.5168,0.0199,0.0552</t>
-  </si>
-  <si>
-    <t>0.2340,0.7458,0.0376,0.0140</t>
-  </si>
-  <si>
-    <t>0.4708,0.3950,0.0338,0.0440</t>
-  </si>
-  <si>
-    <t>0.2414,0.6697,0.0280,0.0438</t>
-  </si>
-  <si>
-    <t>0.2439,0.7055,0.0361,0.0281</t>
-  </si>
-  <si>
-    <t>0.3289,0.5865,0.0340,0.0371</t>
-  </si>
-  <si>
-    <t>0.3266,0.5650,0.0261,0.0450</t>
-  </si>
-  <si>
-    <t>0.1873,0.7083,0.0995,0.0048</t>
-  </si>
-  <si>
-    <t>0.1278,0.5002,0.3663,0.0043</t>
-  </si>
-  <si>
-    <t>0.0834,0.7790,0.1754,0.0052</t>
-  </si>
-  <si>
-    <t>0.2992,0.3205,0.2644,0.0041</t>
-  </si>
-  <si>
-    <t>0.1841,0.7332,0.0855,0.0064</t>
-  </si>
-  <si>
-    <t>0.0194,0.9649,0.0280,0.0015</t>
-  </si>
-  <si>
-    <t>0.0100,0.9795,0.0210,0.0013</t>
-  </si>
-  <si>
-    <t>0.0156,0.9736,0.0187,0.0021</t>
-  </si>
-  <si>
-    <t>0.0184,0.9661,0.0280,0.0025</t>
-  </si>
-  <si>
-    <t>0.0042,0.9898,0.0153,0.0006</t>
-  </si>
-  <si>
-    <t>0.1729,0.7035,0.1202,0.0072</t>
-  </si>
-  <si>
-    <t>0.1589,0.5955,0.1982,0.0031</t>
-  </si>
-  <si>
-    <t>0.1527,0.0433,0.7570,0.0024</t>
-  </si>
-  <si>
-    <t>0.3389,0.3087,0.2241,0.0036</t>
-  </si>
-  <si>
-    <t>0.3446,0.0250,0.6269,0.0039</t>
-  </si>
-  <si>
-    <t>0.3988,0.0249,0.5838,0.0040</t>
-  </si>
-  <si>
-    <t>0.0482,0.1057,0.8260,0.0012</t>
-  </si>
-  <si>
-    <t>0.0232,0.9569,0.0382,0.0031</t>
-  </si>
-  <si>
-    <t>0.2667,0.5859,0.1347,0.0066</t>
-  </si>
-  <si>
-    <t>0.0000,0.4486,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0251,0.9472,0.0489,0.0009</t>
-  </si>
-  <si>
-    <t>0.2149,0.7311,0.0774,0.0272</t>
-  </si>
-  <si>
-    <t>0.1351,0.7993,0.0946,0.0103</t>
-  </si>
-  <si>
-    <t>0.0689,0.9106,0.0317,0.0063</t>
-  </si>
-  <si>
-    <t>0.0112,0.9740,0.0359,0.0011</t>
-  </si>
-  <si>
-    <t>0.0031,0.9647,0.2303,0.0004</t>
-  </si>
-  <si>
-    <t>0.2197,0.1116,0.5398,0.0038</t>
-  </si>
-  <si>
-    <t>0.0987,0.4914,0.4225,0.0043</t>
-  </si>
-  <si>
-    <t>0.5190,0.0267,0.4781,0.0035</t>
-  </si>
-  <si>
-    <t>0.0501,0.7714,0.2490,0.0016</t>
-  </si>
-  <si>
-    <t>0.0025,0.9936,0.0107,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.1258,0.9109,0.0017</t>
-  </si>
-  <si>
-    <t>0.3184,0.6016,0.0633,0.0270</t>
-  </si>
-  <si>
-    <t>0.0106,0.9800,0.0186,0.0011</t>
-  </si>
-  <si>
-    <t>0.0036,0.9916,0.0117,0.0003</t>
-  </si>
-  <si>
-    <t>0.0075,0.9856,0.0133,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.0278,0.9883,0.0004</t>
-  </si>
-  <si>
-    <t>0.0304,0.0688,0.9083,0.0016</t>
-  </si>
-  <si>
-    <t>0.3263,0.1524,0.4189,0.0061</t>
-  </si>
-  <si>
-    <t>0.3629,0.0136,0.6467,0.0035</t>
-  </si>
-  <si>
-    <t>0.0049,0.5960,0.8865,0.0007</t>
-  </si>
-  <si>
-    <t>0.0202,0.1601,0.8862,0.0009</t>
-  </si>
-  <si>
-    <t>0.1753,0.8028,0.0415,0.0142</t>
-  </si>
-  <si>
-    <t>0.3076,0.6304,0.0487,0.0314</t>
-  </si>
-  <si>
-    <t>0.2728,0.6537,0.0285,0.0376</t>
-  </si>
-  <si>
-    <t>0.0026,0.2554,0.9786,0.0009</t>
-  </si>
-  <si>
-    <t>0.2786,0.6719,0.0400,0.0255</t>
-  </si>
-  <si>
-    <t>0.2052,0.6905,0.0220,0.0615</t>
-  </si>
-  <si>
-    <t>0.2426,0.7094,0.0394,0.0299</t>
-  </si>
-  <si>
-    <t>0.0025,0.9095,0.5629,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0475,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.1597,0.9153,0.0008</t>
-  </si>
-  <si>
-    <t>0.0025,0.9598,0.2972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0269,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.0077,0.9807,0.0300,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.2659,0.1159,0.5608,0.0062</t>
-  </si>
-  <si>
-    <t>0.1807,0.6871,0.1249,0.0049</t>
-  </si>
-  <si>
-    <t>0.0020,0.8034,0.8905,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.9796,0.3614,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.8171,0.4300,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0078,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9910,0.2217,0.0000</t>
-  </si>
-  <si>
-    <t>0.6663,0.1046,0.1826,0.0136</t>
-  </si>
-  <si>
-    <t>0.2269,0.2331,0.0156,0.4672</t>
-  </si>
-  <si>
-    <t>0.2800,0.0859,0.0133,0.5260</t>
-  </si>
-  <si>
-    <t>0.3003,0.5212,0.0412,0.1001</t>
-  </si>
-  <si>
-    <t>0.1506,0.7760,0.0506,0.0517</t>
-  </si>
-  <si>
-    <t>0.3533,0.3664,0.0402,0.1608</t>
-  </si>
-  <si>
-    <t>0.0025,0.9645,0.2926,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.9597,0.4711,0.0002</t>
-  </si>
-  <si>
-    <t>0.0079,0.8383,0.5040,0.0008</t>
-  </si>
-  <si>
-    <t>0.0453,0.5997,0.4457,0.0024</t>
-  </si>
-  <si>
-    <t>0.0014,0.9799,0.2101,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.9005,0.3783,0.0008</t>
-  </si>
-  <si>
-    <t>0.2911,0.6472,0.0369,0.0285</t>
-  </si>
-  <si>
-    <t>0.2395,0.7250,0.0328,0.0197</t>
-  </si>
-  <si>
-    <t>0.2471,0.7182,0.0336,0.0210</t>
-  </si>
-  <si>
-    <t>0.2764,0.6339,0.0358,0.0436</t>
-  </si>
-  <si>
-    <t>0.2417,0.7148,0.0435,0.0242</t>
-  </si>
-  <si>
-    <t>0.3405,0.5101,0.0260,0.0644</t>
-  </si>
-  <si>
-    <t>0.3070,0.6175,0.0421,0.0328</t>
-  </si>
-  <si>
-    <t>0.1943,0.7659,0.0307,0.0247</t>
-  </si>
-  <si>
-    <t>0.2522,0.5496,0.0241,0.1227</t>
-  </si>
-  <si>
-    <t>0.3880,0.5433,0.0340,0.0264</t>
-  </si>
-  <si>
-    <t>0.3798,0.5008,0.0280,0.0487</t>
-  </si>
-  <si>
-    <t>0.4031,0.4734,0.0297,0.0458</t>
-  </si>
-  <si>
-    <t>0.3764,0.4983,0.0270,0.0518</t>
-  </si>
-  <si>
-    <t>0.3114,0.6112,0.0324,0.0374</t>
-  </si>
-  <si>
-    <t>0.1896,0.7461,0.0230,0.0357</t>
-  </si>
-  <si>
-    <t>0.4426,0.3396,0.0295,0.0935</t>
-  </si>
-  <si>
-    <t>0.0002,0.0499,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.2589,0.0392,0.6452,0.0023</t>
-  </si>
-  <si>
-    <t>0.3654,0.3687,0.2013,0.0055</t>
-  </si>
-  <si>
-    <t>0.3056,0.0829,0.5312,0.0032</t>
-  </si>
-  <si>
-    <t>0.0078,0.9852,0.0129,0.0019</t>
-  </si>
-  <si>
-    <t>0.0070,0.9863,0.0128,0.0019</t>
-  </si>
-  <si>
-    <t>0.0240,0.9649,0.0151,0.0034</t>
-  </si>
-  <si>
-    <t>0.0336,0.9481,0.0285,0.0046</t>
-  </si>
-  <si>
-    <t>0.0089,0.9832,0.0144,0.0020</t>
-  </si>
-  <si>
-    <t>0.0027,0.9938,0.0081,0.0007</t>
-  </si>
-  <si>
-    <t>0.0308,0.9507,0.0290,0.0040</t>
-  </si>
-  <si>
-    <t>0.1982,0.6544,0.1118,0.0047</t>
-  </si>
-  <si>
-    <t>0.2337,0.1226,0.5613,0.0039</t>
-  </si>
-  <si>
-    <t>0.2732,0.5238,0.1439,0.0057</t>
-  </si>
-  <si>
-    <t>0.0779,0.8714,0.0783,0.0052</t>
-  </si>
-  <si>
-    <t>0.1032,0.8472,0.0773,0.0086</t>
-  </si>
-  <si>
-    <t>0.0060,0.9872,0.0154,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.9964,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.0570,0.9220,0.0342,0.0048</t>
-  </si>
-  <si>
-    <t>0.0009,0.9930,0.0738,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.9916,0.0182,0.0004</t>
-  </si>
-  <si>
-    <t>0.0920,0.8778,0.0468,0.0061</t>
-  </si>
-  <si>
-    <t>0.0730,0.8983,0.0444,0.0075</t>
-  </si>
-  <si>
-    <t>0.1147,0.8458,0.0644,0.0113</t>
-  </si>
-  <si>
-    <t>0.2544,0.6671,0.0352,0.0403</t>
-  </si>
-  <si>
-    <t>0.2689,0.6657,0.0303,0.0314</t>
-  </si>
-  <si>
-    <t>0.1012,0.8799,0.0232,0.0136</t>
-  </si>
-  <si>
-    <t>0.2498,0.6704,0.0269,0.0418</t>
-  </si>
-  <si>
-    <t>0.1838,0.7794,0.0605,0.0140</t>
-  </si>
-  <si>
-    <t>0.2999,0.6578,0.0404,0.0224</t>
-  </si>
-  <si>
-    <t>0.3332,0.6258,0.0502,0.0201</t>
-  </si>
-  <si>
-    <t>0.0126,0.7538,0.5361,0.0011</t>
-  </si>
-  <si>
-    <t>0.0155,0.6075,0.6445,0.0010</t>
-  </si>
-  <si>
-    <t>0.0165,0.6680,0.6745,0.0021</t>
-  </si>
-  <si>
-    <t>0.0401,0.3813,0.6938,0.0021</t>
-  </si>
-  <si>
-    <t>0.2406,0.6269,0.1006,0.0057</t>
-  </si>
-  <si>
-    <t>0.1207,0.7503,0.1385,0.0051</t>
-  </si>
-  <si>
-    <t>0.1986,0.2477,0.4818,0.0048</t>
-  </si>
-  <si>
-    <t>0.1641,0.7370,0.0967,0.0050</t>
-  </si>
-  <si>
-    <t>0.3864,0.4716,0.0587,0.0707</t>
-  </si>
-  <si>
-    <t>0.0489,0.2968,0.0052,0.9022</t>
-  </si>
-  <si>
-    <t>0.1278,0.1908,0.0139,0.7725</t>
-  </si>
-  <si>
-    <t>0.3255,0.4547,0.0397,0.1210</t>
-  </si>
-  <si>
-    <t>0.0005,0.9615,0.6697,0.0001</t>
-  </si>
-  <si>
-    <t>0.1674,0.8005,0.0317,0.0207</t>
-  </si>
-  <si>
-    <t>0.0278,0.9567,0.0234,0.0055</t>
-  </si>
-  <si>
-    <t>0.2479,0.7155,0.0439,0.0209</t>
-  </si>
-  <si>
-    <t>0.1853,0.7815,0.0611,0.0137</t>
-  </si>
-  <si>
-    <t>0.2029,0.7493,0.0718,0.0115</t>
-  </si>
-  <si>
-    <t>0.6718,0.1374,0.1204,0.0176</t>
-  </si>
-  <si>
-    <t>0.3426,0.5921,0.0681,0.0290</t>
-  </si>
-  <si>
-    <t>0.0053,0.4215,0.9509,0.0034</t>
-  </si>
-  <si>
-    <t>0.7520,0.0875,0.1091,0.0127</t>
-  </si>
-  <si>
-    <t>0.7270,0.1394,0.0879,0.0117</t>
-  </si>
-  <si>
-    <t>0.0389,0.9340,0.0501,0.0040</t>
-  </si>
-  <si>
-    <t>0.2171,0.7384,0.0776,0.0121</t>
-  </si>
-  <si>
-    <t>0.1842,0.7666,0.0801,0.0106</t>
-  </si>
-  <si>
-    <t>0.0468,0.9320,0.0361,0.0036</t>
-  </si>
-  <si>
-    <t>0.3816,0.4633,0.1132,0.0058</t>
-  </si>
-  <si>
-    <t>0.1105,0.8611,0.0466,0.0089</t>
-  </si>
-  <si>
-    <t>0.3939,0.5129,0.0363,0.0333</t>
-  </si>
-  <si>
-    <t>0.2729,0.6381,0.0308,0.0414</t>
-  </si>
-  <si>
-    <t>0.2893,0.6710,0.0440,0.0210</t>
-  </si>
-  <si>
-    <t>0.3093,0.5901,0.0346,0.0475</t>
-  </si>
-  <si>
-    <t>0.3486,0.5989,0.0413,0.0237</t>
-  </si>
-  <si>
-    <t>0.1677,0.8044,0.0401,0.0187</t>
-  </si>
-  <si>
-    <t>0.4395,0.4843,0.0451,0.0291</t>
-  </si>
-  <si>
-    <t>0.3355,0.5717,0.0285,0.0388</t>
-  </si>
-  <si>
-    <t>0.0743,0.9022,0.0380,0.0056</t>
-  </si>
-  <si>
-    <t>0.0792,0.8967,0.0328,0.0146</t>
-  </si>
-  <si>
-    <t>0.0697,0.9025,0.0445,0.0075</t>
-  </si>
-  <si>
-    <t>0.2708,0.5815,0.1422,0.0091</t>
-  </si>
-  <si>
-    <t>0.1130,0.8741,0.0267,0.0072</t>
-  </si>
-  <si>
-    <t>0.2105,0.7681,0.0437,0.0128</t>
-  </si>
-  <si>
-    <t>0.1910,0.7719,0.0392,0.0215</t>
-  </si>
-  <si>
-    <t>0.1116,0.8611,0.0361,0.0166</t>
-  </si>
-  <si>
-    <t>0.0001,0.4901,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.2619,0.6992,0.0635,0.0140</t>
-  </si>
-  <si>
-    <t>0.0233,0.0694,0.9183,0.0005</t>
-  </si>
-  <si>
-    <t>0.0170,0.2404,0.8840,0.0012</t>
-  </si>
-  <si>
-    <t>0.1467,0.2022,0.6224,0.0050</t>
-  </si>
-  <si>
-    <t>0.0004,0.0995,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0345,0.1438,0.8692,0.0019</t>
-  </si>
-  <si>
-    <t>0.0119,0.0331,0.9685,0.0006</t>
-  </si>
-  <si>
-    <t>0.0222,0.1118,0.9216,0.0019</t>
-  </si>
-  <si>
-    <t>0.1850,0.4191,0.3372,0.0053</t>
-  </si>
-  <si>
-    <t>0.4282,0.0598,0.4934,0.0077</t>
-  </si>
-  <si>
-    <t>0.2895,0.4772,0.1641,0.0049</t>
-  </si>
-  <si>
-    <t>0.1686,0.6516,0.1594,0.0048</t>
-  </si>
-  <si>
-    <t>0.0778,0.8102,0.1310,0.0038</t>
-  </si>
-  <si>
-    <t>0.2091,0.6626,0.1267,0.0093</t>
-  </si>
-  <si>
-    <t>0.2158,0.6906,0.1126,0.0127</t>
-  </si>
-  <si>
-    <t>0.1237,0.7611,0.1374,0.0065</t>
-  </si>
-  <si>
-    <t>0.0346,0.9521,0.0190,0.0046</t>
-  </si>
-  <si>
-    <t>0.0570,0.9218,0.0316,0.0055</t>
-  </si>
-  <si>
-    <t>0.0329,0.9523,0.0217,0.0041</t>
-  </si>
-  <si>
-    <t>0.1077,0.8562,0.0272,0.0296</t>
-  </si>
-  <si>
-    <t>0.1008,0.8765,0.0242,0.0170</t>
-  </si>
-  <si>
-    <t>0.1540,0.7180,0.0957,0.0026</t>
-  </si>
-  <si>
-    <t>0.2261,0.5997,0.1542,0.0063</t>
-  </si>
-  <si>
-    <t>0.1409,0.7882,0.0843,0.0058</t>
-  </si>
-  <si>
-    <t>0.3394,0.3721,0.1932,0.0045</t>
-  </si>
-  <si>
-    <t>0.2758,0.4744,0.1728,0.0046</t>
-  </si>
-  <si>
-    <t>0.0311,0.4873,0.7230,0.0031</t>
-  </si>
-  <si>
-    <t>0.1244,0.3419,0.4792,0.0039</t>
-  </si>
-  <si>
-    <t>0.1282,0.3427,0.4516,0.0033</t>
-  </si>
-  <si>
-    <t>0.1902,0.2000,0.4787,0.0033</t>
-  </si>
-  <si>
-    <t>0.0407,0.6169,0.3993,0.0016</t>
-  </si>
-  <si>
-    <t>0.2773,0.6278,0.0273,0.0462</t>
-  </si>
-  <si>
-    <t>0.1327,0.8380,0.0253,0.0225</t>
-  </si>
-  <si>
-    <t>0.1524,0.8128,0.0326,0.0237</t>
-  </si>
-  <si>
-    <t>0.2299,0.7282,0.0357,0.0252</t>
-  </si>
-  <si>
-    <t>0.1988,0.7584,0.0344,0.0277</t>
-  </si>
-  <si>
-    <t>0.2120,0.7180,0.0267,0.0377</t>
-  </si>
-  <si>
-    <t>0.1756,0.7639,0.0314,0.0423</t>
-  </si>
-  <si>
-    <t>0.3281,0.6251,0.0405,0.0212</t>
-  </si>
-  <si>
-    <t>0.1910,0.0804,0.6986,0.0077</t>
-  </si>
-  <si>
-    <t>0.1208,0.8311,0.0712,0.0081</t>
-  </si>
-  <si>
-    <t>0.0799,0.8887,0.0507,0.0054</t>
-  </si>
-  <si>
-    <t>0.0030,0.2195,0.9659,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.2180,0.9861,0.0002</t>
-  </si>
-  <si>
-    <t>0.1341,0.1132,0.7042,0.0061</t>
-  </si>
-  <si>
-    <t>0.0003,0.0253,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.1399,0.5069,0.3475,0.0049</t>
-  </si>
-  <si>
-    <t>0.0000,0.0237,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.2241,0.1054,0.5887,0.0051</t>
-  </si>
-  <si>
-    <t>0.0863,0.7843,0.1747,0.0050</t>
-  </si>
-  <si>
-    <t>0.4125,0.3686,0.1455,0.0077</t>
-  </si>
-  <si>
-    <t>0.3656,0.3165,0.2196,0.0059</t>
-  </si>
-  <si>
-    <t>0.3759,0.3959,0.1698,0.0071</t>
-  </si>
-  <si>
-    <t>0.1786,0.7825,0.0284,0.0255</t>
-  </si>
-  <si>
-    <t>0.3107,0.6115,0.0364,0.0340</t>
-  </si>
-  <si>
-    <t>0.2930,0.6028,0.0250,0.0445</t>
-  </si>
-  <si>
-    <t>0.1448,0.8047,0.0254,0.0338</t>
-  </si>
-  <si>
-    <t>0.3943,0.4569,0.0273,0.0540</t>
-  </si>
-  <si>
-    <t>0.2862,0.6430,0.0354,0.0337</t>
-  </si>
-  <si>
-    <t>0.1559,0.7980,0.0230,0.0304</t>
-  </si>
-  <si>
-    <t>0.2225,0.6707,0.0216,0.0553</t>
-  </si>
-  <si>
-    <t>0.0512,0.8348,0.1868,0.0039</t>
-  </si>
-  <si>
-    <t>0.0057,0.4641,0.8951,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.5456,0.7496,0.0014</t>
-  </si>
-  <si>
-    <t>0.1212,0.7703,0.0799,0.0016</t>
-  </si>
-  <si>
-    <t>0.0386,0.1292,0.8398,0.0013</t>
-  </si>
-  <si>
-    <t>0.2258,0.1415,0.5709,0.0065</t>
-  </si>
-  <si>
-    <t>0.1749,0.2453,0.4807,0.0030</t>
-  </si>
-  <si>
-    <t>0.3977,0.0127,0.6257,0.0024</t>
-  </si>
-  <si>
-    <t>0.4606,0.3357,0.0381,0.0556</t>
-  </si>
-  <si>
-    <t>0.1622,0.6128,0.0229,0.2695</t>
-  </si>
-  <si>
-    <t>0.2903,0.5414,0.0264,0.0783</t>
-  </si>
-  <si>
-    <t>0.5082,0.2145,0.0563,0.0990</t>
-  </si>
-  <si>
-    <t>0.0648,0.2536,0.0044,0.8627</t>
-  </si>
-  <si>
-    <t>0.5965,0.2073,0.1526,0.0108</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.1004,0.8636,0.0554,0.0104</t>
+  </si>
+  <si>
+    <t>0.2358,0.4256,0.0217,0.2669</t>
+  </si>
+  <si>
+    <t>0.2382,0.7158,0.0467,0.0255</t>
+  </si>
+  <si>
+    <t>0.5463,0.2493,0.0813,0.0451</t>
+  </si>
+  <si>
+    <t>0.2773,0.5787,0.0214,0.0708</t>
+  </si>
+  <si>
+    <t>0.4162,0.4943,0.0239,0.0266</t>
+  </si>
+  <si>
+    <t>0.2109,0.7659,0.0391,0.0157</t>
+  </si>
+  <si>
+    <t>0.3857,0.5157,0.0338,0.0378</t>
+  </si>
+  <si>
+    <t>0.2200,0.7040,0.0308,0.0420</t>
+  </si>
+  <si>
+    <t>0.2069,0.7401,0.0356,0.0309</t>
+  </si>
+  <si>
+    <t>0.3590,0.5113,0.0313,0.0552</t>
+  </si>
+  <si>
+    <t>0.3563,0.5308,0.0249,0.0436</t>
+  </si>
+  <si>
+    <t>0.1242,0.8114,0.0867,0.0060</t>
+  </si>
+  <si>
+    <t>0.1712,0.4279,0.3665,0.0046</t>
+  </si>
+  <si>
+    <t>0.3044,0.2317,0.3633,0.0043</t>
+  </si>
+  <si>
+    <t>0.3501,0.0743,0.4934,0.0035</t>
+  </si>
+  <si>
+    <t>0.2330,0.6187,0.1132,0.0054</t>
+  </si>
+  <si>
+    <t>0.0122,0.9759,0.0228,0.0013</t>
+  </si>
+  <si>
+    <t>0.0092,0.9819,0.0173,0.0015</t>
+  </si>
+  <si>
+    <t>0.0153,0.9719,0.0244,0.0018</t>
+  </si>
+  <si>
+    <t>0.0183,0.9666,0.0278,0.0025</t>
+  </si>
+  <si>
+    <t>0.0060,0.9877,0.0126,0.0008</t>
+  </si>
+  <si>
+    <t>0.2488,0.5278,0.1962,0.0072</t>
+  </si>
+  <si>
+    <t>0.1783,0.5456,0.2152,0.0030</t>
+  </si>
+  <si>
+    <t>0.1838,0.0167,0.7836,0.0015</t>
+  </si>
+  <si>
+    <t>0.4553,0.0602,0.4434,0.0052</t>
+  </si>
+  <si>
+    <t>0.4253,0.0835,0.4215,0.0049</t>
+  </si>
+  <si>
+    <t>0.5723,0.0142,0.4838,0.0029</t>
+  </si>
+  <si>
+    <t>0.3094,0.0931,0.4841,0.0031</t>
+  </si>
+  <si>
+    <t>0.0155,0.9700,0.0282,0.0023</t>
+  </si>
+  <si>
+    <t>0.2408,0.6761,0.1050,0.0110</t>
+  </si>
+  <si>
+    <t>0.0000,0.1438,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0319,0.9210,0.0775,0.0011</t>
+  </si>
+  <si>
+    <t>0.1717,0.7828,0.0747,0.0158</t>
+  </si>
+  <si>
+    <t>0.1572,0.8007,0.0669,0.0115</t>
+  </si>
+  <si>
+    <t>0.0645,0.9106,0.0382,0.0056</t>
+  </si>
+  <si>
+    <t>0.0202,0.9633,0.0322,0.0026</t>
+  </si>
+  <si>
+    <t>0.0041,0.9371,0.3791,0.0008</t>
+  </si>
+  <si>
+    <t>0.3742,0.0322,0.5614,0.0032</t>
+  </si>
+  <si>
+    <t>0.0476,0.6960,0.3767,0.0025</t>
+  </si>
+  <si>
+    <t>0.3277,0.0294,0.6267,0.0038</t>
+  </si>
+  <si>
+    <t>0.0306,0.7782,0.3144,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.1363,0.0623,0.7533,0.0044</t>
+  </si>
+  <si>
+    <t>0.2459,0.7042,0.0740,0.0161</t>
+  </si>
+  <si>
+    <t>0.0067,0.9882,0.0091,0.0008</t>
+  </si>
+  <si>
+    <t>0.0070,0.9802,0.0358,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.9930,0.0101,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.1904,0.9823,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.1879,0.9487,0.0007</t>
+  </si>
+  <si>
+    <t>0.3371,0.0468,0.5843,0.0055</t>
+  </si>
+  <si>
+    <t>0.3085,0.0091,0.7124,0.0021</t>
+  </si>
+  <si>
+    <t>0.0023,0.2719,0.9708,0.0002</t>
+  </si>
+  <si>
+    <t>0.0425,0.5458,0.5590,0.0023</t>
+  </si>
+  <si>
+    <t>0.1696,0.8085,0.0403,0.0137</t>
+  </si>
+  <si>
+    <t>0.2859,0.6808,0.0481,0.0178</t>
+  </si>
+  <si>
+    <t>0.1682,0.8027,0.0286,0.0225</t>
+  </si>
+  <si>
+    <t>0.0012,0.1581,0.9903,0.0005</t>
+  </si>
+  <si>
+    <t>0.3107,0.6228,0.0371,0.0319</t>
+  </si>
+  <si>
+    <t>0.2415,0.6618,0.0222,0.0473</t>
+  </si>
+  <si>
+    <t>0.1977,0.7487,0.0363,0.0356</t>
+  </si>
+  <si>
+    <t>0.0011,0.9802,0.2551,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0778,0.9930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0647,0.0512,0.8571,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.9549,0.4031,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.1280,0.9617,0.0005</t>
+  </si>
+  <si>
+    <t>0.0045,0.9878,0.0234,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4532,0.1871,0.2735,0.0052</t>
+  </si>
+  <si>
+    <t>0.1379,0.7370,0.1208,0.0045</t>
+  </si>
+  <si>
+    <t>0.0002,0.4035,0.9931,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9765,0.3613,0.0001</t>
+  </si>
+  <si>
+    <t>0.0245,0.7852,0.3796,0.0015</t>
+  </si>
+  <si>
+    <t>0.0005,0.9970,0.0186,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9907,0.1041,0.0001</t>
+  </si>
+  <si>
+    <t>0.5802,0.2029,0.1247,0.0364</t>
+  </si>
+  <si>
+    <t>0.1933,0.3493,0.0186,0.4643</t>
+  </si>
+  <si>
+    <t>0.1831,0.2441,0.0158,0.5947</t>
+  </si>
+  <si>
+    <t>0.3330,0.4548,0.0474,0.1132</t>
+  </si>
+  <si>
+    <t>0.4689,0.3002,0.0824,0.0701</t>
+  </si>
+  <si>
+    <t>0.3456,0.4288,0.0486,0.1278</t>
+  </si>
+  <si>
+    <t>0.0065,0.9620,0.1324,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.9556,0.4499,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.6201,0.9211,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.6971,0.6768,0.0014</t>
+  </si>
+  <si>
+    <t>0.0017,0.9563,0.4090,0.0002</t>
+  </si>
+  <si>
+    <t>0.0199,0.8881,0.1650,0.0009</t>
+  </si>
+  <si>
+    <t>0.3419,0.6102,0.0405,0.0222</t>
+  </si>
+  <si>
+    <t>0.1520,0.8180,0.0268,0.0205</t>
+  </si>
+  <si>
+    <t>0.2467,0.7173,0.0381,0.0224</t>
+  </si>
+  <si>
+    <t>0.1812,0.7702,0.0374,0.0312</t>
+  </si>
+  <si>
+    <t>0.2351,0.7231,0.0396,0.0239</t>
+  </si>
+  <si>
+    <t>0.2774,0.6188,0.0255,0.0483</t>
+  </si>
+  <si>
+    <t>0.3098,0.6117,0.0353,0.0332</t>
+  </si>
+  <si>
+    <t>0.1740,0.7873,0.0295,0.0245</t>
+  </si>
+  <si>
+    <t>0.3004,0.5037,0.0228,0.1076</t>
+  </si>
+  <si>
+    <t>0.3741,0.5502,0.0347,0.0322</t>
+  </si>
+  <si>
+    <t>0.3552,0.5042,0.0266,0.0628</t>
+  </si>
+  <si>
+    <t>0.5000,0.3450,0.0260,0.0456</t>
+  </si>
+  <si>
+    <t>0.4005,0.4505,0.0308,0.0621</t>
+  </si>
+  <si>
+    <t>0.2102,0.7160,0.0296,0.0439</t>
+  </si>
+  <si>
+    <t>0.2799,0.6425,0.0281,0.0374</t>
+  </si>
+  <si>
+    <t>0.5092,0.2678,0.0193,0.0746</t>
+  </si>
+  <si>
+    <t>0.0001,0.1479,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.4541,0.0237,0.5362,0.0019</t>
+  </si>
+  <si>
+    <t>0.3840,0.3403,0.1934,0.0052</t>
+  </si>
+  <si>
+    <t>0.2287,0.0386,0.6816,0.0023</t>
+  </si>
+  <si>
+    <t>0.0074,0.9851,0.0148,0.0018</t>
+  </si>
+  <si>
+    <t>0.0114,0.9790,0.0178,0.0019</t>
+  </si>
+  <si>
+    <t>0.0194,0.9696,0.0167,0.0031</t>
+  </si>
+  <si>
+    <t>0.0342,0.9499,0.0239,0.0048</t>
+  </si>
+  <si>
+    <t>0.0091,0.9823,0.0165,0.0014</t>
+  </si>
+  <si>
+    <t>0.0065,0.9877,0.0105,0.0015</t>
+  </si>
+  <si>
+    <t>0.0312,0.9539,0.0222,0.0043</t>
+  </si>
+  <si>
+    <t>0.0882,0.8448,0.0880,0.0042</t>
+  </si>
+  <si>
+    <t>0.2560,0.2624,0.3986,0.0052</t>
+  </si>
+  <si>
+    <t>0.0796,0.8660,0.0742,0.0038</t>
+  </si>
+  <si>
+    <t>0.1357,0.7887,0.0973,0.0104</t>
+  </si>
+  <si>
+    <t>0.1307,0.8341,0.0615,0.0105</t>
+  </si>
+  <si>
+    <t>0.0039,0.9899,0.0168,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.9945,0.0071,0.0002</t>
+  </si>
+  <si>
+    <t>0.1339,0.8140,0.0629,0.0061</t>
+  </si>
+  <si>
+    <t>0.0008,0.9954,0.0342,0.0001</t>
+  </si>
+  <si>
+    <t>0.0091,0.9797,0.0248,0.0009</t>
+  </si>
+  <si>
+    <t>0.1303,0.8413,0.0475,0.0077</t>
+  </si>
+  <si>
+    <t>0.0458,0.9296,0.0388,0.0049</t>
+  </si>
+  <si>
+    <t>0.0937,0.8677,0.0625,0.0072</t>
+  </si>
+  <si>
+    <t>0.1858,0.7247,0.0243,0.0554</t>
+  </si>
+  <si>
+    <t>0.1908,0.7591,0.0308,0.0300</t>
+  </si>
+  <si>
+    <t>0.1563,0.8288,0.0308,0.0111</t>
+  </si>
+  <si>
+    <t>0.3426,0.5800,0.0357,0.0350</t>
+  </si>
+  <si>
+    <t>0.1901,0.7719,0.0505,0.0182</t>
+  </si>
+  <si>
+    <t>0.2426,0.7188,0.0347,0.0214</t>
+  </si>
+  <si>
+    <t>0.3982,0.5074,0.0587,0.0374</t>
+  </si>
+  <si>
+    <t>0.0168,0.7846,0.4154,0.0012</t>
+  </si>
+  <si>
+    <t>0.0062,0.3474,0.9128,0.0004</t>
+  </si>
+  <si>
+    <t>0.0304,0.3551,0.7693,0.0022</t>
+  </si>
+  <si>
+    <t>0.1045,0.4389,0.3365,0.0014</t>
+  </si>
+  <si>
+    <t>0.2356,0.6360,0.0938,0.0043</t>
+  </si>
+  <si>
+    <t>0.1731,0.5496,0.2228,0.0055</t>
+  </si>
+  <si>
+    <t>0.4843,0.1598,0.2847,0.0058</t>
+  </si>
+  <si>
+    <t>0.3520,0.3957,0.1374,0.0037</t>
+  </si>
+  <si>
+    <t>0.2934,0.5528,0.0494,0.1084</t>
+  </si>
+  <si>
+    <t>0.0428,0.0622,0.0042,0.9580</t>
+  </si>
+  <si>
+    <t>0.0658,0.2064,0.0071,0.8911</t>
+  </si>
+  <si>
+    <t>0.3348,0.3920,0.0362,0.1340</t>
+  </si>
+  <si>
+    <t>0.0002,0.9807,0.6494,0.0000</t>
+  </si>
+  <si>
+    <t>0.1277,0.8233,0.0233,0.0352</t>
+  </si>
+  <si>
+    <t>0.0478,0.9302,0.0358,0.0075</t>
+  </si>
+  <si>
+    <t>0.2188,0.7586,0.0431,0.0139</t>
+  </si>
+  <si>
+    <t>0.1510,0.8156,0.0565,0.0121</t>
+  </si>
+  <si>
+    <t>0.2719,0.6507,0.0869,0.0116</t>
+  </si>
+  <si>
+    <t>0.6413,0.1520,0.1070,0.0325</t>
+  </si>
+  <si>
+    <t>0.4218,0.4987,0.0611,0.0266</t>
+  </si>
+  <si>
+    <t>0.0039,0.1291,0.9790,0.0034</t>
+  </si>
+  <si>
+    <t>0.7413,0.0905,0.0620,0.0239</t>
+  </si>
+  <si>
+    <t>0.6587,0.1856,0.0740,0.0225</t>
+  </si>
+  <si>
+    <t>0.0401,0.9378,0.0380,0.0043</t>
+  </si>
+  <si>
+    <t>0.1702,0.7931,0.0604,0.0097</t>
+  </si>
+  <si>
+    <t>0.1637,0.7988,0.0630,0.0122</t>
+  </si>
+  <si>
+    <t>0.0662,0.9032,0.0514,0.0051</t>
+  </si>
+  <si>
+    <t>0.1684,0.7782,0.0777,0.0089</t>
+  </si>
+  <si>
+    <t>0.1451,0.8237,0.0539,0.0085</t>
+  </si>
+  <si>
+    <t>0.3101,0.5901,0.0325,0.0449</t>
+  </si>
+  <si>
+    <t>0.2861,0.6705,0.0472,0.0219</t>
+  </si>
+  <si>
+    <t>0.3230,0.6127,0.0412,0.0293</t>
+  </si>
+  <si>
+    <t>0.3399,0.5231,0.0326,0.0635</t>
+  </si>
+  <si>
+    <t>0.3010,0.6534,0.0529,0.0208</t>
+  </si>
+  <si>
+    <t>0.1583,0.8154,0.0408,0.0170</t>
+  </si>
+  <si>
+    <t>0.4044,0.5323,0.0479,0.0223</t>
+  </si>
+  <si>
+    <t>0.2955,0.6172,0.0254,0.0396</t>
+  </si>
+  <si>
+    <t>0.0630,0.9152,0.0345,0.0047</t>
+  </si>
+  <si>
+    <t>0.1045,0.8666,0.0454,0.0111</t>
+  </si>
+  <si>
+    <t>0.0619,0.9158,0.0350,0.0071</t>
+  </si>
+  <si>
+    <t>0.2144,0.7514,0.0628,0.0110</t>
+  </si>
+  <si>
+    <t>0.1085,0.8743,0.0288,0.0104</t>
+  </si>
+  <si>
+    <t>0.1918,0.7857,0.0515,0.0092</t>
+  </si>
+  <si>
+    <t>0.2281,0.7276,0.0390,0.0249</t>
+  </si>
+  <si>
+    <t>0.0684,0.9118,0.0269,0.0117</t>
+  </si>
+  <si>
+    <t>0.0000,0.4971,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.2020,0.7675,0.0573,0.0116</t>
+  </si>
+  <si>
+    <t>0.0187,0.0571,0.9334,0.0004</t>
+  </si>
+  <si>
+    <t>0.0268,0.1931,0.8532,0.0015</t>
+  </si>
+  <si>
+    <t>0.4647,0.1136,0.3689,0.0075</t>
+  </si>
+  <si>
+    <t>0.0005,0.2411,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.0273,0.2581,0.8429,0.0020</t>
+  </si>
+  <si>
+    <t>0.0302,0.0269,0.9403,0.0008</t>
+  </si>
+  <si>
+    <t>0.0057,0.2341,0.9572,0.0009</t>
+  </si>
+  <si>
+    <t>0.1663,0.5971,0.1940,0.0052</t>
+  </si>
+  <si>
+    <t>0.3018,0.0583,0.5964,0.0048</t>
+  </si>
+  <si>
+    <t>0.1246,0.7752,0.1154,0.0047</t>
+  </si>
+  <si>
+    <t>0.1404,0.6611,0.1736,0.0042</t>
+  </si>
+  <si>
+    <t>0.1329,0.7216,0.1231,0.0049</t>
+  </si>
+  <si>
+    <t>0.2289,0.6647,0.1081,0.0100</t>
+  </si>
+  <si>
+    <t>0.2807,0.5803,0.1242,0.0101</t>
+  </si>
+  <si>
+    <t>0.2482,0.5370,0.1644,0.0055</t>
+  </si>
+  <si>
+    <t>0.0660,0.9157,0.0284,0.0071</t>
+  </si>
+  <si>
+    <t>0.0499,0.9296,0.0310,0.0045</t>
+  </si>
+  <si>
+    <t>0.0613,0.9189,0.0288,0.0066</t>
+  </si>
+  <si>
+    <t>0.1291,0.8395,0.0326,0.0231</t>
+  </si>
+  <si>
+    <t>0.1225,0.8569,0.0274,0.0159</t>
+  </si>
+  <si>
+    <t>0.3475,0.3533,0.1972,0.0034</t>
+  </si>
+  <si>
+    <t>0.4205,0.2635,0.2335,0.0070</t>
+  </si>
+  <si>
+    <t>0.2369,0.6331,0.1176,0.0073</t>
+  </si>
+  <si>
+    <t>0.4068,0.1228,0.3816,0.0039</t>
+  </si>
+  <si>
+    <t>0.0885,0.8550,0.0827,0.0052</t>
+  </si>
+  <si>
+    <t>0.0309,0.6180,0.5940,0.0030</t>
+  </si>
+  <si>
+    <t>0.1865,0.3162,0.4316,0.0049</t>
+  </si>
+  <si>
+    <t>0.0609,0.7930,0.1530,0.0016</t>
+  </si>
+  <si>
+    <t>0.1638,0.2404,0.4329,0.0022</t>
+  </si>
+  <si>
+    <t>0.0382,0.7735,0.2132,0.0012</t>
+  </si>
+  <si>
+    <t>0.3436,0.5404,0.0272,0.0479</t>
+  </si>
+  <si>
+    <t>0.2244,0.7202,0.0308,0.0337</t>
+  </si>
+  <si>
+    <t>0.1546,0.7955,0.0308,0.0342</t>
+  </si>
+  <si>
+    <t>0.2220,0.7255,0.0282,0.0291</t>
+  </si>
+  <si>
+    <t>0.2039,0.7480,0.0331,0.0307</t>
+  </si>
+  <si>
+    <t>0.2124,0.7165,0.0258,0.0381</t>
+  </si>
+  <si>
+    <t>0.2762,0.6403,0.0309,0.0416</t>
+  </si>
+  <si>
+    <t>0.2615,0.6791,0.0314,0.0274</t>
+  </si>
+  <si>
+    <t>0.4040,0.0477,0.5441,0.0078</t>
+  </si>
+  <si>
+    <t>0.1200,0.8177,0.0838,0.0094</t>
+  </si>
+  <si>
+    <t>0.1583,0.7800,0.0740,0.0080</t>
+  </si>
+  <si>
+    <t>0.0056,0.1947,0.9533,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.1667,0.9872,0.0001</t>
+  </si>
+  <si>
+    <t>0.1308,0.2944,0.5506,0.0047</t>
+  </si>
+  <si>
+    <t>0.0022,0.0108,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.2231,0.3339,0.3581,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.0265,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.1229,0.0561,0.7893,0.0039</t>
+  </si>
+  <si>
+    <t>0.0187,0.6648,0.6714,0.0026</t>
+  </si>
+  <si>
+    <t>0.5677,0.1075,0.2715,0.0050</t>
+  </si>
+  <si>
+    <t>0.2339,0.4630,0.2632,0.0073</t>
+  </si>
+  <si>
+    <t>0.3677,0.4307,0.1487,0.0077</t>
+  </si>
+  <si>
+    <t>0.1862,0.7834,0.0274,0.0202</t>
+  </si>
+  <si>
+    <t>0.2784,0.6639,0.0327,0.0281</t>
+  </si>
+  <si>
+    <t>0.4068,0.5097,0.0324,0.0305</t>
+  </si>
+  <si>
+    <t>0.2269,0.7467,0.0493,0.0137</t>
+  </si>
+  <si>
+    <t>0.2002,0.7005,0.0239,0.0647</t>
+  </si>
+  <si>
+    <t>0.1964,0.7677,0.0331,0.0233</t>
+  </si>
+  <si>
+    <t>0.0957,0.8760,0.0200,0.0212</t>
+  </si>
+  <si>
+    <t>0.2773,0.5966,0.0263,0.0587</t>
+  </si>
+  <si>
+    <t>0.0314,0.8852,0.1567,0.0019</t>
+  </si>
+  <si>
+    <t>0.0027,0.3307,0.9577,0.0003</t>
+  </si>
+  <si>
+    <t>0.0047,0.6188,0.8479,0.0006</t>
+  </si>
+  <si>
+    <t>0.2157,0.4149,0.2818,0.0037</t>
+  </si>
+  <si>
+    <t>0.0397,0.0434,0.9031,0.0008</t>
+  </si>
+  <si>
+    <t>0.2607,0.3744,0.3208,0.0070</t>
+  </si>
+  <si>
+    <t>0.1070,0.5189,0.3671,0.0028</t>
+  </si>
+  <si>
+    <t>0.3442,0.0798,0.4833,0.0042</t>
+  </si>
+  <si>
+    <t>0.4427,0.3316,0.0377,0.0787</t>
+  </si>
+  <si>
+    <t>0.1107,0.7710,0.0238,0.1591</t>
+  </si>
+  <si>
+    <t>0.1199,0.6948,0.0187,0.2279</t>
+  </si>
+  <si>
+    <t>0.2610,0.4088,0.0268,0.2244</t>
+  </si>
+  <si>
+    <t>0.0591,0.1793,0.0041,0.9024</t>
+  </si>
+  <si>
+    <t>0.5576,0.2275,0.1601,0.0127</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,10 +2026,10 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,10 +2054,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>262</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>262</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>262</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>262</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>262</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>262</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>262</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>262</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>262</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>262</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>262</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,10 +3342,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>262</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3426,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>262</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>262</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>262</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>262</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>262</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>262</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>262</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>262</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3930,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>262</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>262</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>262</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,10 +4098,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4210,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>262</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>262</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>262</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>262</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>262</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>262</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,10 +4322,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>262</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>262</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>262</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4784,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>262</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>262</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>262</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>262</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>262</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>262</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>262</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>262</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>262</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>262</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>262</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>262</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>262</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>262</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,10 +5274,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>262</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>262</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>262</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>262</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>262</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
